--- a/data/objetivos_por_marca_pepsico.xlsx
+++ b/data/objetivos_por_marca_pepsico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\a subir mas analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C28E4086-8A2D-46FE-97FF-904DEE302F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75919510-493E-44C9-AA8B-A0EAAE698E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Marca</t>
   </si>
@@ -28,102 +28,30 @@
     <t>Jan-26 Obj</t>
   </si>
   <si>
-    <t>Jan-26 Cobertura</t>
-  </si>
-  <si>
-    <t>Jan-26 Cump %</t>
-  </si>
-  <si>
     <t>Feb-26 Obj</t>
   </si>
   <si>
-    <t>Feb-26 Cobertura</t>
-  </si>
-  <si>
-    <t>Feb-26 Cump %</t>
-  </si>
-  <si>
     <t>Mar-26 Obj</t>
   </si>
   <si>
-    <t>Mar-26 Cobertura</t>
-  </si>
-  <si>
-    <t>Mar-26 Cump %</t>
-  </si>
-  <si>
     <t>Apr-26 Obj</t>
   </si>
   <si>
-    <t>Apr-26 Cobertura</t>
-  </si>
-  <si>
-    <t>Apr-26 Cump %</t>
-  </si>
-  <si>
     <t>Cheetos</t>
   </si>
   <si>
-    <t>103.38%</t>
-  </si>
-  <si>
-    <t>100.88%</t>
-  </si>
-  <si>
-    <t>94.70%</t>
-  </si>
-  <si>
-    <t>69.44%</t>
-  </si>
-  <si>
     <t>Doritos</t>
   </si>
   <si>
-    <t>99.16%</t>
-  </si>
-  <si>
-    <t>99.33%</t>
-  </si>
-  <si>
-    <t>98.83%</t>
-  </si>
-  <si>
-    <t>78.62%</t>
-  </si>
-  <si>
     <t>Lays</t>
   </si>
   <si>
-    <t>99.46%</t>
-  </si>
-  <si>
-    <t>98.91%</t>
-  </si>
-  <si>
-    <t>98.63%</t>
-  </si>
-  <si>
-    <t>76.44%</t>
-  </si>
-  <si>
     <t>Pehuamar</t>
   </si>
   <si>
     <t>Pep</t>
   </si>
   <si>
-    <t>100.23%</t>
-  </si>
-  <si>
-    <t>98.99%</t>
-  </si>
-  <si>
-    <t>81.75%</t>
-  </si>
-  <si>
-    <t>22.95%</t>
-  </si>
-  <si>
     <t>Quaker</t>
   </si>
   <si>
@@ -133,29 +61,30 @@
     <t>Twistos</t>
   </si>
   <si>
-    <t>100.27%</t>
-  </si>
-  <si>
-    <t>99.54%</t>
-  </si>
-  <si>
-    <t>100.09%</t>
-  </si>
-  <si>
-    <t>37.21%</t>
+    <t>Jun-26 Obj</t>
+  </si>
+  <si>
+    <t>May-26 Obj</t>
+  </si>
+  <si>
+    <t>3D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -172,7 +101,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -180,16 +109,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{F8AC5132-CEB0-4425-9D6C-3018EC6F0D29}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -489,327 +434,242 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0.85634606904955313</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.88000511498810463</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.93097394338118022</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.83509671077654524</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.89036152635719901</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.91246056782334384</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B3" s="4">
+        <v>0.84517311535337125</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.87650647977795415</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.91192982456140348</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.96357408399366096</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.97999999999999987</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.99290220820189279</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B4" s="4">
+        <v>0.93432166531275396</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.95307454401268832</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.97702625837320567</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.97999999999999987</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.99211356466876977</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B5" s="4">
+        <v>0.93486940373679939</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.95572563838223634</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.97999999999999987</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.98580441640378547</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B6" s="4">
+        <v>0.27754830219333876</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.2607276130055512</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.27061825358851671</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.26358577654516641</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.24071597167584582</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.19400630914826497</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B7" s="4">
+        <v>0.49677156783103166</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.59290302775574943</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.68267125996810207</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.58338795562599055</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.26982848151062155</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0.22239747634069401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4">
+        <v>8.179254559873117E-2</v>
+      </c>
+      <c r="D8" s="4">
+        <v>9.0295215311004789E-2</v>
+      </c>
+      <c r="E8" s="4">
+        <v>8.1071220285261494E-2</v>
+      </c>
+      <c r="F8" s="4">
+        <v>8.3273013375295038E-2</v>
+      </c>
+      <c r="G8" s="4">
+        <v>8.7539432176656148E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4">
+        <v>0.11808650277557492</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.25631763157894738</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="G9" s="4">
+        <v>5.28391167192429E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="1">
-        <v>78.86</v>
-      </c>
-      <c r="C2">
-        <v>81.5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1">
-        <v>82.14</v>
-      </c>
-      <c r="F2">
-        <v>82.9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="1">
-        <v>83.86</v>
-      </c>
-      <c r="I2">
-        <v>79.400000000000006</v>
-      </c>
-      <c r="J2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="1">
-        <v>80.239999999999995</v>
-      </c>
-      <c r="L2">
-        <v>55.7</v>
-      </c>
-      <c r="M2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="1">
-        <v>96.97</v>
-      </c>
-      <c r="C3">
-        <v>96.2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1">
-        <v>97.53</v>
-      </c>
-      <c r="F3">
-        <v>96.9</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="1">
-        <v>98</v>
-      </c>
-      <c r="I3">
-        <v>96.9</v>
-      </c>
-      <c r="J3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="1">
-        <v>97.56</v>
-      </c>
-      <c r="L3">
-        <v>76.7</v>
-      </c>
-      <c r="M3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="1">
-        <v>94.07</v>
-      </c>
-      <c r="C4">
-        <v>93.6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="1">
-        <v>94.12</v>
-      </c>
-      <c r="F4">
-        <v>93.1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="1">
-        <v>94.9</v>
-      </c>
-      <c r="I4">
-        <v>93.6</v>
-      </c>
-      <c r="J4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="1">
-        <v>94.29</v>
-      </c>
-      <c r="L4">
-        <v>72.099999999999994</v>
-      </c>
-      <c r="M4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5">
-        <v>21.4</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5">
-        <v>19</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5">
-        <v>18.2</v>
-      </c>
-      <c r="K5" s="1"/>
-      <c r="L5">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="1">
-        <v>60.37</v>
-      </c>
-      <c r="C6">
-        <v>60.5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="1">
-        <v>61.2</v>
-      </c>
-      <c r="F6">
-        <v>60.6</v>
-      </c>
-      <c r="G6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="1">
-        <v>62.34</v>
-      </c>
-      <c r="I6">
-        <v>51</v>
-      </c>
-      <c r="J6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="1">
-        <v>53.12</v>
-      </c>
-      <c r="L6">
-        <v>12.2</v>
-      </c>
-      <c r="M6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7">
-        <v>2.4</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7">
-        <v>3.4</v>
-      </c>
-      <c r="H7" s="1"/>
-      <c r="I7">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="K7" s="1"/>
-      <c r="L7">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8">
-        <v>27.7</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8">
-        <v>9.1</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="1">
-        <v>76.91</v>
-      </c>
-      <c r="C9">
-        <v>77.099999999999994</v>
-      </c>
-      <c r="D9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="1">
-        <v>77.95</v>
-      </c>
-      <c r="F9">
-        <v>77.599999999999994</v>
-      </c>
-      <c r="G9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="1">
-        <v>79.37</v>
-      </c>
-      <c r="I9">
-        <v>79.400000000000006</v>
-      </c>
-      <c r="J9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="1">
-        <v>80.319999999999993</v>
-      </c>
-      <c r="L9">
-        <v>29.9</v>
-      </c>
-      <c r="M9" t="s">
-        <v>40</v>
+      <c r="B10" s="4">
+        <v>0.74542508854589762</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0.76720132434575727</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.80835253588516753</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.84603004754358169</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.38405664830841857</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.41640378548895901</v>
       </c>
     </row>
   </sheetData>
